--- a/data/trans_orig/P79A5_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P79A5_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene resuelto el retraso en los pagos de los impuestos relacionados con vehículos en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si tiene resuelto el retraso en los pagos de los impuestos relacionados con vehículos, IBI, etc en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10096</t>
+          <t>11783</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11717</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>18783</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>15247</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18595</t>
+          <t>20408</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>21098</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>21098</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>21098</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,27 +1411,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>460</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>70,78%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1549,34 +1549,34 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>86,89%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3474</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3506</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>357</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8512</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8512</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8512</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>595</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>595</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>539</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>925</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>700</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>700</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>700</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>700</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,27 +2783,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>701</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,27 +3126,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>19124</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12900</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18191</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>15887</t>
+          <t>17890</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3196,27 +3196,27 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>32917</t>
+          <t>37014</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28917</t>
+          <t>32145</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34078</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>18191</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>18191</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18191</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15887</t>
+          <t>17890</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15887</t>
+          <t>17890</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15887</t>
+          <t>17890</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>34078</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>34078</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>34078</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>34241</t>
+          <t>36725</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27691</t>
+          <t>29680</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38472</t>
+          <t>41681</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>30550</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>28921</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34664</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>64791</t>
+          <t>71291</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>56683</t>
+          <t>61709</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>70548</t>
+          <t>77258</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,51%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8791</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15341</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>14155</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26194</t>
+          <t>29704</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
